--- a/قائمة الوحدات الخاصة بالفوج20252026/قائمة جهة نابل فوج قرمبالية المدينة وحدة حنبعل.xlsx
+++ b/قائمة الوحدات الخاصة بالفوج20252026/قائمة جهة نابل فوج قرمبالية المدينة وحدة حنبعل.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="20">
   <si>
     <t>المعرف</t>
   </si>
@@ -68,6 +68,12 @@
   </si>
   <si>
     <t>ملازم قائد الوحدة</t>
+  </si>
+  <si>
+    <t>code_unite</t>
+  </si>
+  <si>
+    <t>RCHT</t>
   </si>
 </sst>
 </file>
@@ -443,12 +449,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="9" max="9" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>18</v>
+      </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -480,9 +489,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>19</v>
       </c>
       <c r="B2">
         <v>900006957</v>
@@ -515,9 +524,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>19</v>
       </c>
       <c r="B3">
         <v>900005516</v>
@@ -553,7 +562,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:K1 A2:K3" numberStoredAsText="1"/>
+    <ignoredError sqref="B1:K1 B3:K3 B2:K2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>